--- a/data/trans_orig/P33B_R2-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/P33B_R2-Provincia-trans_orig.xlsx
@@ -725,32 +725,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>34544</t>
+          <t>34272</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>24877</t>
+          <t>24941</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>47707</t>
+          <t>46013</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>11,09%</t>
+          <t>10,75%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>7,99%</t>
+          <t>7,82%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>15,32%</t>
+          <t>14,43%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -760,32 +760,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>38565</t>
+          <t>42158</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>30591</t>
+          <t>33275</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>47112</t>
+          <t>50722</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>13,32%</t>
+          <t>13,34%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>10,56%</t>
+          <t>10,53%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>16,27%</t>
+          <t>16,05%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -795,32 +795,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>73109</t>
+          <t>76430</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>59957</t>
+          <t>64835</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>89229</t>
+          <t>91548</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>12,16%</t>
+          <t>12,04%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>9,97%</t>
+          <t>10,21%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>14,84%</t>
+          <t>14,42%</t>
         </is>
       </c>
     </row>
@@ -838,32 +838,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>276899</t>
+          <t>284573</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>263736</t>
+          <t>272832</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>286566</t>
+          <t>293904</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>88,91%</t>
+          <t>89,25%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>84,68%</t>
+          <t>85,57%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>92,01%</t>
+          <t>92,18%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -873,32 +873,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>251070</t>
+          <t>273903</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>242523</t>
+          <t>265339</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>259044</t>
+          <t>282786</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>86,68%</t>
+          <t>86,66%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>83,73%</t>
+          <t>83,95%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>89,44%</t>
+          <t>89,47%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -908,32 +908,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>527968</t>
+          <t>558476</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>511848</t>
+          <t>543358</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>541120</t>
+          <t>570071</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>87,84%</t>
+          <t>87,96%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>85,16%</t>
+          <t>85,58%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>90,03%</t>
+          <t>89,79%</t>
         </is>
       </c>
     </row>
@@ -951,17 +951,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>311443</t>
+          <t>318845</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>311443</t>
+          <t>318845</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>311443</t>
+          <t>318845</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -986,17 +986,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>289635</t>
+          <t>316061</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>289635</t>
+          <t>316061</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>289635</t>
+          <t>316061</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1021,17 +1021,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>601077</t>
+          <t>634906</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>601077</t>
+          <t>634906</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>601077</t>
+          <t>634906</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1068,32 +1068,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>50040</t>
+          <t>50825</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>34607</t>
+          <t>36759</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>67981</t>
+          <t>68853</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>9,65%</t>
+          <t>9,58%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>6,68%</t>
+          <t>6,93%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>13,11%</t>
+          <t>12,98%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1103,32 +1103,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>78334</t>
+          <t>82057</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>65663</t>
+          <t>68981</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>92371</t>
+          <t>98200</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>15,21%</t>
+          <t>15,02%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>12,75%</t>
+          <t>12,62%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>17,94%</t>
+          <t>17,97%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1138,32 +1138,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>128373</t>
+          <t>132882</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>108141</t>
+          <t>111035</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>151876</t>
+          <t>158404</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>12,42%</t>
+          <t>12,34%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>10,46%</t>
+          <t>10,31%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>14,7%</t>
+          <t>14,71%</t>
         </is>
       </c>
     </row>
@@ -1181,32 +1181,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>468350</t>
+          <t>479822</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>450409</t>
+          <t>461794</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>483783</t>
+          <t>493888</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>90,35%</t>
+          <t>90,42%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>86,89%</t>
+          <t>87,02%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>93,32%</t>
+          <t>93,07%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1216,32 +1216,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>436635</t>
+          <t>464437</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>422598</t>
+          <t>448294</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>449306</t>
+          <t>477513</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>84,79%</t>
+          <t>84,98%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>82,06%</t>
+          <t>82,03%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>87,25%</t>
+          <t>87,38%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1251,32 +1251,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>904986</t>
+          <t>944259</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>881483</t>
+          <t>918737</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>925218</t>
+          <t>966106</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>87,58%</t>
+          <t>87,66%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>85,3%</t>
+          <t>85,29%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>89,54%</t>
+          <t>89,69%</t>
         </is>
       </c>
     </row>
@@ -1294,17 +1294,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>518390</t>
+          <t>530647</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>518390</t>
+          <t>530647</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>518390</t>
+          <t>530647</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1329,17 +1329,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>514969</t>
+          <t>546494</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>514969</t>
+          <t>546494</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>514969</t>
+          <t>546494</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1364,17 +1364,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>1033359</t>
+          <t>1077141</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>1033359</t>
+          <t>1077141</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>1033359</t>
+          <t>1077141</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1411,32 +1411,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>41141</t>
+          <t>42094</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>31606</t>
+          <t>32231</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>53179</t>
+          <t>53840</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>13,02%</t>
+          <t>13,32%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>10,0%</t>
+          <t>10,2%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>16,83%</t>
+          <t>17,04%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1446,32 +1446,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>78902</t>
+          <t>81378</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>67021</t>
+          <t>67545</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>92413</t>
+          <t>94805</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>22,63%</t>
+          <t>22,87%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>19,22%</t>
+          <t>18,98%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>26,51%</t>
+          <t>26,64%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1481,32 +1481,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>120043</t>
+          <t>123472</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>103578</t>
+          <t>105957</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>136961</t>
+          <t>140598</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>18,06%</t>
+          <t>18,38%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>15,58%</t>
+          <t>15,77%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>20,61%</t>
+          <t>20,93%</t>
         </is>
       </c>
     </row>
@@ -1524,32 +1524,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>274909</t>
+          <t>273899</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>262871</t>
+          <t>262153</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>284444</t>
+          <t>283762</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>86,98%</t>
+          <t>86,68%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>83,17%</t>
+          <t>82,96%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>90,0%</t>
+          <t>89,8%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1559,32 +1559,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>269723</t>
+          <t>274464</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>256212</t>
+          <t>261037</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>281604</t>
+          <t>288297</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>77,37%</t>
+          <t>77,13%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>73,49%</t>
+          <t>73,36%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>80,78%</t>
+          <t>81,02%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1594,32 +1594,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>544632</t>
+          <t>548364</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>527714</t>
+          <t>531238</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>561097</t>
+          <t>565879</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>81,94%</t>
+          <t>81,62%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>79,39%</t>
+          <t>79,07%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>84,42%</t>
+          <t>84,23%</t>
         </is>
       </c>
     </row>
@@ -1637,17 +1637,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>316050</t>
+          <t>315993</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>316050</t>
+          <t>315993</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>316050</t>
+          <t>315993</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1672,17 +1672,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>348625</t>
+          <t>355842</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>348625</t>
+          <t>355842</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>348625</t>
+          <t>355842</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1707,17 +1707,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>664675</t>
+          <t>671836</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>664675</t>
+          <t>671836</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>664675</t>
+          <t>671836</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1754,32 +1754,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>51477</t>
+          <t>59283</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>37752</t>
+          <t>43385</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>68135</t>
+          <t>78474</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>16,47%</t>
+          <t>15,89%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>12,08%</t>
+          <t>11,63%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>21,8%</t>
+          <t>21,03%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1789,32 +1789,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>77470</t>
+          <t>87121</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>47892</t>
+          <t>72851</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>101426</t>
+          <t>104029</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>16,28%</t>
+          <t>20,65%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>10,07%</t>
+          <t>17,26%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>21,32%</t>
+          <t>24,65%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1824,32 +1824,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>128947</t>
+          <t>146404</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>92053</t>
+          <t>125118</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>154546</t>
+          <t>173739</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>16,36%</t>
+          <t>18,41%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>11,68%</t>
+          <t>15,74%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>19,61%</t>
+          <t>21,85%</t>
         </is>
       </c>
     </row>
@@ -1867,32 +1867,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>261080</t>
+          <t>313862</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>244422</t>
+          <t>294671</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>274805</t>
+          <t>329760</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>83,53%</t>
+          <t>84,11%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>78,2%</t>
+          <t>78,97%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>87,92%</t>
+          <t>88,37%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1902,32 +1902,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>398248</t>
+          <t>334840</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>374292</t>
+          <t>317932</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>427826</t>
+          <t>349110</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>83,72%</t>
+          <t>79,35%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>78,68%</t>
+          <t>75,35%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>89,93%</t>
+          <t>82,74%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1937,32 +1937,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>659327</t>
+          <t>648703</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>633728</t>
+          <t>621368</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>696221</t>
+          <t>669989</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>83,64%</t>
+          <t>81,59%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>80,39%</t>
+          <t>78,15%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>88,32%</t>
+          <t>84,26%</t>
         </is>
       </c>
     </row>
@@ -1980,17 +1980,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>312557</t>
+          <t>373145</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>312557</t>
+          <t>373145</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>312557</t>
+          <t>373145</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -2015,17 +2015,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>475718</t>
+          <t>421961</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>475718</t>
+          <t>421961</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>475718</t>
+          <t>421961</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2050,17 +2050,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>788274</t>
+          <t>795107</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>788274</t>
+          <t>795107</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>788274</t>
+          <t>795107</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2097,32 +2097,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>14324</t>
+          <t>15270</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>9484</t>
+          <t>10126</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>20821</t>
+          <t>22784</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>8,01%</t>
+          <t>7,42%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>5,31%</t>
+          <t>4,92%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>11,65%</t>
+          <t>11,08%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2132,32 +2132,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>23559</t>
+          <t>24474</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>18373</t>
+          <t>18837</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>30175</t>
+          <t>30915</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>11,31%</t>
+          <t>10,79%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>8,82%</t>
+          <t>8,3%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>14,49%</t>
+          <t>13,63%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2167,32 +2167,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>37883</t>
+          <t>39744</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>30844</t>
+          <t>31602</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>46208</t>
+          <t>48254</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>9,79%</t>
+          <t>9,19%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>7,97%</t>
+          <t>7,31%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>11,94%</t>
+          <t>11,16%</t>
         </is>
       </c>
     </row>
@@ -2210,32 +2210,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>164418</t>
+          <t>190395</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>157921</t>
+          <t>182881</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>169258</t>
+          <t>195539</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>91,99%</t>
+          <t>92,58%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>88,35%</t>
+          <t>88,92%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>94,69%</t>
+          <t>95,08%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2245,32 +2245,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>184715</t>
+          <t>202349</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>178099</t>
+          <t>195908</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>189901</t>
+          <t>207986</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>88,69%</t>
+          <t>89,21%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>85,51%</t>
+          <t>86,37%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>91,18%</t>
+          <t>91,7%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2280,32 +2280,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>349133</t>
+          <t>392744</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>340808</t>
+          <t>384234</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>356172</t>
+          <t>400886</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>90,21%</t>
+          <t>90,81%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>88,06%</t>
+          <t>88,84%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>92,03%</t>
+          <t>92,69%</t>
         </is>
       </c>
     </row>
@@ -2323,17 +2323,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>178742</t>
+          <t>205665</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>178742</t>
+          <t>205665</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>178742</t>
+          <t>205665</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2358,17 +2358,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>208274</t>
+          <t>226823</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>208274</t>
+          <t>226823</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>208274</t>
+          <t>226823</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2393,17 +2393,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>387016</t>
+          <t>432488</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>387016</t>
+          <t>432488</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>387016</t>
+          <t>432488</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2440,32 +2440,32 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>41124</t>
+          <t>40827</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>31633</t>
+          <t>31896</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>51576</t>
+          <t>52096</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>15,25%</t>
+          <t>15,08%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>11,73%</t>
+          <t>11,78%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>19,13%</t>
+          <t>19,24%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2475,32 +2475,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>71381</t>
+          <t>73171</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>61062</t>
+          <t>62257</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>83506</t>
+          <t>84402</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>27,77%</t>
+          <t>27,74%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>23,75%</t>
+          <t>23,6%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>32,49%</t>
+          <t>32,0%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2510,32 +2510,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>112505</t>
+          <t>113998</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>98479</t>
+          <t>98709</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>127139</t>
+          <t>128565</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>21,36%</t>
+          <t>21,33%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>18,7%</t>
+          <t>18,47%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>24,14%</t>
+          <t>24,06%</t>
         </is>
       </c>
     </row>
@@ -2553,32 +2553,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>228512</t>
+          <t>229880</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>218060</t>
+          <t>218611</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>238003</t>
+          <t>238811</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>84,75%</t>
+          <t>84,92%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>80,87%</t>
+          <t>80,76%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>88,27%</t>
+          <t>88,22%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2588,32 +2588,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>185675</t>
+          <t>190579</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>173550</t>
+          <t>179348</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>195994</t>
+          <t>201493</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>72,23%</t>
+          <t>72,26%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>67,51%</t>
+          <t>68,0%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>76,25%</t>
+          <t>76,4%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2623,32 +2623,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>414187</t>
+          <t>420459</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>399553</t>
+          <t>405892</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>428213</t>
+          <t>435748</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>78,64%</t>
+          <t>78,67%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>75,86%</t>
+          <t>75,94%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>81,3%</t>
+          <t>81,53%</t>
         </is>
       </c>
     </row>
@@ -2666,17 +2666,17 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>269636</t>
+          <t>270707</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>269636</t>
+          <t>270707</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>269636</t>
+          <t>270707</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2701,17 +2701,17 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>257056</t>
+          <t>263750</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>257056</t>
+          <t>263750</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>257056</t>
+          <t>263750</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2736,17 +2736,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>526692</t>
+          <t>534457</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>526692</t>
+          <t>534457</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>526692</t>
+          <t>534457</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2783,32 +2783,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>78606</t>
+          <t>90818</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>63251</t>
+          <t>74477</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>97768</t>
+          <t>111705</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>12,61%</t>
+          <t>12,64%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>10,15%</t>
+          <t>10,36%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>15,69%</t>
+          <t>15,54%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2818,32 +2818,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>162217</t>
+          <t>198811</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>79947</t>
+          <t>177620</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>219536</t>
+          <t>221645</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>19,1%</t>
+          <t>25,75%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>9,41%</t>
+          <t>23,01%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>25,85%</t>
+          <t>28,71%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2853,32 +2853,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>240822</t>
+          <t>289629</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>154905</t>
+          <t>261120</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>291135</t>
+          <t>322680</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>16,35%</t>
+          <t>19,43%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>10,52%</t>
+          <t>17,52%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>19,77%</t>
+          <t>21,65%</t>
         </is>
       </c>
     </row>
@@ -2896,32 +2896,32 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>544644</t>
+          <t>627787</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>525482</t>
+          <t>606900</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>559999</t>
+          <t>644128</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>87,39%</t>
+          <t>87,36%</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>84,31%</t>
+          <t>84,46%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>89,85%</t>
+          <t>89,64%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2931,32 +2931,32 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>687048</t>
+          <t>573246</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>629729</t>
+          <t>550412</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>769318</t>
+          <t>594437</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>80,9%</t>
+          <t>74,25%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>74,15%</t>
+          <t>71,29%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>90,59%</t>
+          <t>76,99%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2966,32 +2966,32 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>1231692</t>
+          <t>1201033</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1181379</t>
+          <t>1167982</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1317609</t>
+          <t>1229542</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>83,65%</t>
+          <t>80,57%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>80,23%</t>
+          <t>78,35%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>89,48%</t>
+          <t>82,48%</t>
         </is>
       </c>
     </row>
@@ -3009,17 +3009,17 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>623250</t>
+          <t>718605</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>623250</t>
+          <t>718605</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>623250</t>
+          <t>718605</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3044,17 +3044,17 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>849265</t>
+          <t>772057</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>849265</t>
+          <t>772057</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>849265</t>
+          <t>772057</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3079,17 +3079,17 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>1472514</t>
+          <t>1490662</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>1472514</t>
+          <t>1490662</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>1472514</t>
+          <t>1490662</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3126,32 +3126,32 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>142540</t>
+          <t>159333</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>65637</t>
+          <t>137461</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>203173</t>
+          <t>181952</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>15,35%</t>
+          <t>19,96%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>7,07%</t>
+          <t>17,22%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>21,88%</t>
+          <t>22,8%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3161,32 +3161,32 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>217498</t>
+          <t>251103</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>198053</t>
+          <t>228507</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>237657</t>
+          <t>270722</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>30,4%</t>
+          <t>30,23%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>27,68%</t>
+          <t>27,51%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>33,22%</t>
+          <t>32,59%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3196,32 +3196,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>360038</t>
+          <t>410436</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>220130</t>
+          <t>381066</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>433532</t>
+          <t>444717</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>21,9%</t>
+          <t>25,2%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>13,39%</t>
+          <t>23,4%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>26,37%</t>
+          <t>27,31%</t>
         </is>
       </c>
     </row>
@@ -3239,32 +3239,32 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>786180</t>
+          <t>638739</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>725547</t>
+          <t>616120</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>863083</t>
+          <t>660611</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>84,65%</t>
+          <t>80,04%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>78,12%</t>
+          <t>77,2%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>92,93%</t>
+          <t>82,78%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3274,32 +3274,32 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>497894</t>
+          <t>579506</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>477735</t>
+          <t>559887</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>517339</t>
+          <t>602102</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>69,6%</t>
+          <t>69,77%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>66,78%</t>
+          <t>67,41%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>72,32%</t>
+          <t>72,49%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3309,32 +3309,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>1284074</t>
+          <t>1218245</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1210580</t>
+          <t>1183964</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1423982</t>
+          <t>1247615</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>78,1%</t>
+          <t>74,8%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>73,63%</t>
+          <t>72,69%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>86,61%</t>
+          <t>76,6%</t>
         </is>
       </c>
     </row>
@@ -3352,17 +3352,17 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>928720</t>
+          <t>798072</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>928720</t>
+          <t>798072</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>928720</t>
+          <t>798072</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -3387,17 +3387,17 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>715392</t>
+          <t>830609</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>715392</t>
+          <t>830609</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>715392</t>
+          <t>830609</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -3422,17 +3422,17 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>1644112</t>
+          <t>1628681</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>1644112</t>
+          <t>1628681</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>1644112</t>
+          <t>1628681</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -3469,32 +3469,32 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>453796</t>
+          <t>492721</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>354325</t>
+          <t>453359</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>505079</t>
+          <t>534440</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>13,12%</t>
+          <t>13,95%</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>10,24%</t>
+          <t>12,84%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>14,6%</t>
+          <t>15,13%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3504,32 +3504,32 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>747925</t>
+          <t>840273</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>596729</t>
+          <t>796552</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>819588</t>
+          <t>882039</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
-          <t>20,44%</t>
+          <t>22,51%</t>
         </is>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>16,31%</t>
+          <t>21,33%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>22,4%</t>
+          <t>23,62%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3539,32 +3539,32 @@
       </c>
       <c r="R28" s="2" t="inlineStr">
         <is>
-          <t>1201720</t>
+          <t>1332994</t>
         </is>
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>1064786</t>
+          <t>1274926</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>1300366</t>
+          <t>1392435</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
         <is>
-          <t>16,88%</t>
+          <t>18,35%</t>
         </is>
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>14,96%</t>
+          <t>17,55%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>18,27%</t>
+          <t>19,17%</t>
         </is>
       </c>
     </row>
@@ -3582,32 +3582,32 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>3004991</t>
+          <t>3038959</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>2953708</t>
+          <t>2997240</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>3104462</t>
+          <t>3078321</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>86,88%</t>
+          <t>86,05%</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>85,4%</t>
+          <t>84,87%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>89,76%</t>
+          <t>87,16%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3617,32 +3617,32 @@
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>2911007</t>
+          <t>2893325</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>2839344</t>
+          <t>2851559</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>3062203</t>
+          <t>2937046</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>79,56%</t>
+          <t>77,49%</t>
         </is>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>77,6%</t>
+          <t>76,38%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>83,69%</t>
+          <t>78,67%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3652,32 +3652,32 @@
       </c>
       <c r="R29" s="2" t="inlineStr">
         <is>
-          <t>5915999</t>
+          <t>5932285</t>
         </is>
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>5817353</t>
+          <t>5872844</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>6052933</t>
+          <t>5990353</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
         <is>
-          <t>83,12%</t>
+          <t>81,65%</t>
         </is>
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>81,73%</t>
+          <t>80,83%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>85,04%</t>
+          <t>82,45%</t>
         </is>
       </c>
     </row>
@@ -3695,17 +3695,17 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>3458787</t>
+          <t>3531680</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>3458787</t>
+          <t>3531680</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>3458787</t>
+          <t>3531680</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3730,17 +3730,17 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>3658932</t>
+          <t>3733598</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>3658932</t>
+          <t>3733598</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>3658932</t>
+          <t>3733598</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3765,17 +3765,17 @@
       </c>
       <c r="R30" s="2" t="inlineStr">
         <is>
-          <t>7117719</t>
+          <t>7265279</t>
         </is>
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>7117719</t>
+          <t>7265279</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>7117719</t>
+          <t>7265279</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
